--- a/input_processing/clean_excel_files_PL/reg_education.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_education.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="77">
   <si>
     <t>Description</t>
   </si>
@@ -160,7 +160,7 @@
     <t>PL10</t>
   </si>
   <si>
-    <t>Year_transformed_E1a</t>
+    <t>Year_transformed</t>
   </si>
   <si>
     <t>Y2021</t>
@@ -181,7 +181,7 @@
     <t>Dag_sq</t>
   </si>
   <si>
-    <t>Dcpst_Partnered</t>
+    <t>Dcpst_Partnered_L1</t>
   </si>
   <si>
     <t>Deh_c4_High_L1</t>
@@ -199,10 +199,7 @@
     <t>Dnc02_L1</t>
   </si>
   <si>
-    <t>Year_transformed_E1b</t>
-  </si>
-  <si>
-    <t>Year_transformed_sq_E1b</t>
+    <t>Year_transformed_sq</t>
   </si>
   <si>
     <t>Dgn_Low</t>
@@ -226,10 +223,10 @@
     <t>PL10_</t>
   </si>
   <si>
-    <t>Year_transformed_E2a_</t>
-  </si>
-  <si>
-    <t>Year_transformed_sq_E2a_</t>
+    <t>Year_transformed_</t>
+  </si>
+  <si>
+    <t>Year_transformed_sq_</t>
   </si>
   <si>
     <t>Y2022_</t>
@@ -459,7 +456,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="1">
-        <v>0.1278079341096533</v>
+        <v>0.12780809107537372</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -467,7 +464,7 @@
         <v>29</v>
       </c>
       <c r="F5" s="1">
-        <v>1261.9796268026462</v>
+        <v>1261.9896304095846</v>
       </c>
     </row>
     <row r="6">
@@ -483,7 +480,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="1">
-        <v>-9996768.4089201912</v>
+        <v>-9996766.6098325625</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +524,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="1">
-        <v>0.65300855498024257</v>
+        <v>0.65310647393739163</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -535,7 +532,7 @@
         <v>29</v>
       </c>
       <c r="F10" s="1">
-        <v>2576.0390105313213</v>
+        <v>2578.6548040088637</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +548,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="1">
-        <v>-4629614.1524004778</v>
+        <v>-4628307.7023530435</v>
       </c>
     </row>
     <row r="12">
@@ -697,64 +694,64 @@
         <v>33</v>
       </c>
       <c r="B2" s="1">
-        <v>-0.1154130784674412</v>
+        <v>-0.11540812849724091</v>
       </c>
       <c r="C2" s="1">
-        <v>0.00081797764701363105</v>
+        <v>0.00081797798092229966</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.7068656753733759e-06</v>
+        <v>-2.7036726652774942e-06</v>
       </c>
       <c r="E2" s="1">
-        <v>3.3094277273074548e-05</v>
+        <v>3.308977954328624e-05</v>
       </c>
       <c r="F2" s="1">
-        <v>-4.4720422582351855e-05</v>
+        <v>-4.4717239179398711e-05</v>
       </c>
       <c r="G2" s="1">
-        <v>7.2998040196351979e-06</v>
+        <v>7.2892696431545597e-06</v>
       </c>
       <c r="H2" s="1">
-        <v>-3.9968160425402462e-05</v>
+        <v>-3.997005669872945e-05</v>
       </c>
       <c r="I2" s="1">
-        <v>1.4785283925948056e-06</v>
+        <v>1.1520171180203152e-06</v>
       </c>
       <c r="J2" s="1">
-        <v>8.4108566866397262e-05</v>
+        <v>8.3937465188436579e-05</v>
       </c>
       <c r="K2" s="1">
-        <v>5.6313829347900151e-05</v>
+        <v>5.6141883848614689e-05</v>
       </c>
       <c r="L2" s="1">
-        <v>0.00016046451498451659</v>
+        <v>0.00016029371313877063</v>
       </c>
       <c r="M2" s="1">
-        <v>-5.3481821714562623e-05</v>
+        <v>-5.3477029643163578e-05</v>
       </c>
       <c r="N2" s="1">
-        <v>-2.9904709081966595e-05</v>
+        <v>-2.9903678057351367e-05</v>
       </c>
       <c r="O2" s="1">
-        <v>-5.7648771016927882e-05</v>
+        <v>-5.7647224451053648e-05</v>
       </c>
       <c r="P2" s="1">
-        <v>-7.283453152536852e-05</v>
+        <v>-7.2832730994053344e-05</v>
       </c>
       <c r="Q2" s="1">
-        <v>-2.3893983448080121e-06</v>
+        <v>-2.3899475033690707e-06</v>
       </c>
       <c r="R2" s="1">
-        <v>-3.4331258980053799e-05</v>
+        <v>-3.4331981893189511e-05</v>
       </c>
       <c r="S2" s="1">
-        <v>1.1216810635136852e-05</v>
+        <v>1.1223884414369564e-05</v>
       </c>
       <c r="T2" s="1">
-        <v>7.5485767162471271e-05</v>
+        <v>7.5491958015186996e-05</v>
       </c>
       <c r="U2" s="1">
-        <v>-0.00035346415509443388</v>
+        <v>-0.00035333537279305682</v>
       </c>
     </row>
     <row r="3">
@@ -762,64 +759,64 @@
         <v>34</v>
       </c>
       <c r="B3" s="1">
-        <v>1.2957419112895525</v>
+        <v>1.2957359274959608</v>
       </c>
       <c r="C3" s="1">
-        <v>-2.7068656753733759e-06</v>
+        <v>-2.7036726652774942e-06</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0022020431538180077</v>
+        <v>0.0022020383004254344</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.0024234193675592699</v>
+        <v>-0.0024234129350171078</v>
       </c>
       <c r="F3" s="1">
-        <v>0.00040286424118256265</v>
+        <v>0.00040285965393646069</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.00012985448455004938</v>
+        <v>-0.00012984009523376965</v>
       </c>
       <c r="H3" s="1">
-        <v>0.00046317924143947191</v>
+        <v>0.00046317867832141452</v>
       </c>
       <c r="I3" s="1">
-        <v>-1.2415563076253954e-05</v>
+        <v>-1.2075308218660733e-05</v>
       </c>
       <c r="J3" s="1">
-        <v>0.00035123617093761898</v>
+        <v>0.00035141362650097509</v>
       </c>
       <c r="K3" s="1">
-        <v>0.0004529064984716061</v>
+        <v>0.00045308314299351174</v>
       </c>
       <c r="L3" s="1">
-        <v>0.00072104263333432929</v>
+        <v>0.00072121708751817122</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.00011219925060916656</v>
+        <v>-0.00011220450394892542</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.0001042606635717337</v>
+        <v>-0.00010426163871430846</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.00013016800957580885</v>
+        <v>-0.00013017023904562941</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.00016217791179779298</v>
+        <v>-0.00016217959861866173</v>
       </c>
       <c r="Q3" s="1">
-        <v>-1.208998261038657e-06</v>
+        <v>-1.208141924974749e-06</v>
       </c>
       <c r="R3" s="1">
-        <v>0.000273253830093214</v>
+        <v>0.0002732542606388149</v>
       </c>
       <c r="S3" s="1">
-        <v>0.00036658305620450304</v>
+        <v>0.00036657448774936319</v>
       </c>
       <c r="T3" s="1">
-        <v>0.00054973838711235186</v>
+        <v>0.00054972589987033714</v>
       </c>
       <c r="U3" s="1">
-        <v>-0.03692271780738493</v>
+        <v>-0.03692283013729368</v>
       </c>
     </row>
     <row r="4">
@@ -827,64 +824,64 @@
         <v>35</v>
       </c>
       <c r="B4" s="1">
-        <v>-1.4122885004196659</v>
+        <v>-1.4122811401234101</v>
       </c>
       <c r="C4" s="1">
-        <v>3.3094277273074548e-05</v>
+        <v>3.308977954328624e-05</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.0024234193675592699</v>
+        <v>-0.0024234129350171078</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0027598721425315803</v>
+        <v>0.0027598638212591713</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.00068248216342328303</v>
+        <v>-0.0006824766046116626</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00035710905519114981</v>
+        <v>0.00035709087838994066</v>
       </c>
       <c r="H4" s="1">
-        <v>-0.00050651014475873446</v>
+        <v>-0.00050650960985188301</v>
       </c>
       <c r="I4" s="1">
-        <v>1.9740427384624812e-05</v>
+        <v>1.9282550138703347e-05</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.00018777519336392291</v>
+        <v>-0.00018801348703617723</v>
       </c>
       <c r="K4" s="1">
-        <v>-0.00022839075843606848</v>
+        <v>-0.00022862838672402849</v>
       </c>
       <c r="L4" s="1">
-        <v>-0.00049827710955895228</v>
+        <v>-0.00049851226117220496</v>
       </c>
       <c r="M4" s="1">
-        <v>0.00014256370933706224</v>
+        <v>0.00014257083825890138</v>
       </c>
       <c r="N4" s="1">
-        <v>0.00011769018389180558</v>
+        <v>0.00011769163802135803</v>
       </c>
       <c r="O4" s="1">
-        <v>0.00015135740510381201</v>
+        <v>0.00015136043983673443</v>
       </c>
       <c r="P4" s="1">
-        <v>0.000184829284897799</v>
+        <v>0.00018483143272084515</v>
       </c>
       <c r="Q4" s="1">
-        <v>8.0144183034979409e-07</v>
+        <v>8.0050792744101179e-07</v>
       </c>
       <c r="R4" s="1">
-        <v>-0.00030746077219194479</v>
+        <v>-0.00030746206680863294</v>
       </c>
       <c r="S4" s="1">
-        <v>-0.00036755045939226849</v>
+        <v>-0.00036753997000179423</v>
       </c>
       <c r="T4" s="1">
-        <v>-0.00057680297638266695</v>
+        <v>-0.00057678801123166659</v>
       </c>
       <c r="U4" s="1">
-        <v>0.040298963170004795</v>
+        <v>0.040299111998440593</v>
       </c>
     </row>
     <row r="5">
@@ -892,64 +889,64 @@
         <v>36</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.152939290186449</v>
+        <v>-0.15294164777043273</v>
       </c>
       <c r="C5" s="1">
-        <v>-4.4720422582351855e-05</v>
+        <v>-4.4717239179398711e-05</v>
       </c>
       <c r="D5" s="1">
-        <v>0.00040286424118256265</v>
+        <v>0.00040285965393646069</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.00068248216342328303</v>
+        <v>-0.0006824766046116626</v>
       </c>
       <c r="F5" s="1">
-        <v>0.0013576480718448837</v>
+        <v>0.0013576450092065181</v>
       </c>
       <c r="G5" s="1">
-        <v>-0.0022379154383646437</v>
+        <v>-0.0022379054681529744</v>
       </c>
       <c r="H5" s="1">
-        <v>8.8878010526591885e-05</v>
+        <v>8.8879532812661871e-05</v>
       </c>
       <c r="I5" s="1">
-        <v>-2.5770514211424528e-05</v>
+        <v>-2.5549696068152602e-05</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.00036122400902767178</v>
+        <v>-0.00036110913459292196</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.00051702059522755006</v>
+        <v>-0.00051690526699295857</v>
       </c>
       <c r="L5" s="1">
-        <v>-0.00052019016625287368</v>
+        <v>-0.00052007537134602213</v>
       </c>
       <c r="M5" s="1">
-        <v>-5.3350474790514598e-05</v>
+        <v>-5.3353815278029673e-05</v>
       </c>
       <c r="N5" s="1">
-        <v>-2.8132410777834702e-05</v>
+        <v>-2.8132893629264169e-05</v>
       </c>
       <c r="O5" s="1">
-        <v>-3.1376406888952279e-06</v>
+        <v>-3.1391155333347284e-06</v>
       </c>
       <c r="P5" s="1">
-        <v>-3.9756716503010084e-05</v>
+        <v>-3.9757652974542349e-05</v>
       </c>
       <c r="Q5" s="1">
-        <v>4.8291225436379202e-06</v>
+        <v>4.8293673665650966e-06</v>
       </c>
       <c r="R5" s="1">
-        <v>6.8480303847401336e-06</v>
+        <v>6.8487392504180955e-06</v>
       </c>
       <c r="S5" s="1">
-        <v>-0.00011198311530407051</v>
+        <v>-0.00011198644406670193</v>
       </c>
       <c r="T5" s="1">
-        <v>-8.2459364852011455e-05</v>
+        <v>-8.2463408827555644e-05</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.0061227718274840092</v>
+        <v>-0.0061228179805968563</v>
       </c>
     </row>
     <row r="6">
@@ -957,64 +954,64 @@
         <v>37</v>
       </c>
       <c r="B6" s="1">
-        <v>0.6229628817816748</v>
+        <v>0.62296515382328688</v>
       </c>
       <c r="C6" s="1">
-        <v>7.2998040196351979e-06</v>
+        <v>7.2892696431545597e-06</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.00012985448455004938</v>
+        <v>-0.00012984009523376965</v>
       </c>
       <c r="E6" s="1">
-        <v>0.00035710905519114981</v>
+        <v>0.00035709087838994066</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.0022379154383646437</v>
+        <v>-0.0022379054681529744</v>
       </c>
       <c r="G6" s="1">
-        <v>0.010100424535457706</v>
+        <v>0.010100398970254573</v>
       </c>
       <c r="H6" s="1">
-        <v>0.00065895428157763947</v>
+        <v>0.00065894877155407076</v>
       </c>
       <c r="I6" s="1">
-        <v>7.316774603645558e-05</v>
+        <v>7.2931855106376587e-05</v>
       </c>
       <c r="J6" s="1">
-        <v>0.0002387031239584829</v>
+        <v>0.00023857686161543896</v>
       </c>
       <c r="K6" s="1">
-        <v>0.00052291412364882097</v>
+        <v>0.00052278651984069124</v>
       </c>
       <c r="L6" s="1">
-        <v>0.00020503189694934568</v>
+        <v>0.00020490541156619466</v>
       </c>
       <c r="M6" s="1">
-        <v>5.7636201607992089e-05</v>
+        <v>5.7639053290283653e-05</v>
       </c>
       <c r="N6" s="1">
-        <v>5.7975000388511827e-05</v>
+        <v>5.7973359016564831e-05</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.00011482808083704721</v>
+        <v>-0.00011482804605330508</v>
       </c>
       <c r="P6" s="1">
-        <v>0.00010122345015018601</v>
+        <v>0.00010122456430900568</v>
       </c>
       <c r="Q6" s="1">
-        <v>-6.9327022591181471e-06</v>
+        <v>-6.9333247933733855e-06</v>
       </c>
       <c r="R6" s="1">
-        <v>3.0484888558718142e-05</v>
+        <v>3.0486836260596719e-05</v>
       </c>
       <c r="S6" s="1">
-        <v>0.00063330289302006184</v>
+        <v>0.00063330689260060902</v>
       </c>
       <c r="T6" s="1">
-        <v>0.00030295609418096717</v>
+        <v>0.00030296141407699218</v>
       </c>
       <c r="U6" s="1">
-        <v>0.0011061800288674857</v>
+        <v>0.0011060926501959465</v>
       </c>
     </row>
     <row r="7">
@@ -1022,64 +1019,64 @@
         <v>38</v>
       </c>
       <c r="B7" s="1">
-        <v>0.052479047783440903</v>
+        <v>0.052482439396915735</v>
       </c>
       <c r="C7" s="1">
-        <v>-3.9968160425402462e-05</v>
+        <v>-3.997005669872945e-05</v>
       </c>
       <c r="D7" s="1">
-        <v>0.00046317924143947191</v>
+        <v>0.00046317867832141452</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.00050651014475873446</v>
+        <v>-0.00050650960985188301</v>
       </c>
       <c r="F7" s="1">
-        <v>8.8878010526591885e-05</v>
+        <v>8.8879532812661871e-05</v>
       </c>
       <c r="G7" s="1">
-        <v>0.00065895428157763947</v>
+        <v>0.00065894877155407076</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0020914033418458528</v>
+        <v>0.0020914105257831702</v>
       </c>
       <c r="I7" s="1">
-        <v>-2.4446744939342619e-05</v>
+        <v>-2.47221915891117e-05</v>
       </c>
       <c r="J7" s="1">
-        <v>-1.4677537181929901e-05</v>
+        <v>-1.4819374999715371e-05</v>
       </c>
       <c r="K7" s="1">
-        <v>2.6954642827969145e-05</v>
+        <v>2.6812528631533242e-05</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.00027869788053019699</v>
+        <v>-0.00027883862833362428</v>
       </c>
       <c r="M7" s="1">
-        <v>0.00010139106771783041</v>
+        <v>0.00010139433747728623</v>
       </c>
       <c r="N7" s="1">
-        <v>5.5212105297375324e-05</v>
+        <v>5.5211966803084744e-05</v>
       </c>
       <c r="O7" s="1">
-        <v>3.3958497758565433e-05</v>
+        <v>3.3957744106144581e-05</v>
       </c>
       <c r="P7" s="1">
-        <v>6.7300361626277706e-05</v>
+        <v>6.7297822361575988e-05</v>
       </c>
       <c r="Q7" s="1">
-        <v>4.6302088779231923e-06</v>
+        <v>4.6306955903849755e-06</v>
       </c>
       <c r="R7" s="1">
-        <v>0.00021615168277011815</v>
+        <v>0.0002161491637605005</v>
       </c>
       <c r="S7" s="1">
-        <v>0.00054262593131322936</v>
+        <v>0.00054263020370422851</v>
       </c>
       <c r="T7" s="1">
-        <v>0.00030734071911156513</v>
+        <v>0.00030734486552616656</v>
       </c>
       <c r="U7" s="1">
-        <v>-0.0096372462023258457</v>
+        <v>-0.0096371073941605087</v>
       </c>
     </row>
     <row r="8">
@@ -1087,64 +1084,64 @@
         <v>39</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.036847513796885875</v>
+        <v>-0.03688220100959768</v>
       </c>
       <c r="C8" s="1">
-        <v>1.4785283925948056e-06</v>
+        <v>1.1520171180203152e-06</v>
       </c>
       <c r="D8" s="1">
-        <v>-1.2415563076253954e-05</v>
+        <v>-1.2075308218660733e-05</v>
       </c>
       <c r="E8" s="1">
-        <v>1.9740427384624812e-05</v>
+        <v>1.9282550138703347e-05</v>
       </c>
       <c r="F8" s="1">
-        <v>-2.5770514211424528e-05</v>
+        <v>-2.5549696068152602e-05</v>
       </c>
       <c r="G8" s="1">
-        <v>7.316774603645558e-05</v>
+        <v>7.2931855106376587e-05</v>
       </c>
       <c r="H8" s="1">
-        <v>-2.4446744939342619e-05</v>
+        <v>-2.47221915891117e-05</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0014405258864269071</v>
+        <v>0.0014404973214927807</v>
       </c>
       <c r="J8" s="1">
-        <v>0.00076495029675020441</v>
+        <v>0.0007647424821385666</v>
       </c>
       <c r="K8" s="1">
-        <v>0.00076985634131825054</v>
+        <v>0.00076960684787524033</v>
       </c>
       <c r="L8" s="1">
-        <v>0.00076955426923134738</v>
+        <v>0.0007693061705854005</v>
       </c>
       <c r="M8" s="1">
-        <v>-2.3848524889332769e-05</v>
+        <v>-2.3854174988041708e-05</v>
       </c>
       <c r="N8" s="1">
-        <v>1.8699201394508307e-06</v>
+        <v>1.8716898087021595e-06</v>
       </c>
       <c r="O8" s="1">
-        <v>-6.8636897057276346e-06</v>
+        <v>-6.8500681719295853e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>-2.0931870345764609e-06</v>
+        <v>-1.945489972192345e-06</v>
       </c>
       <c r="Q8" s="1">
-        <v>5.5045763964354166e-06</v>
+        <v>5.4735451849653149e-06</v>
       </c>
       <c r="R8" s="1">
-        <v>-1.4287261285218268e-05</v>
+        <v>-1.4161555506849398e-05</v>
       </c>
       <c r="S8" s="1">
-        <v>-3.9049729114890084e-05</v>
+        <v>-3.8942385664020827e-05</v>
       </c>
       <c r="T8" s="1">
-        <v>-6.4911689274599937e-05</v>
+        <v>-6.4762110773726429e-05</v>
       </c>
       <c r="U8" s="1">
-        <v>-0.00062355856854435371</v>
+        <v>-0.00062800191405550142</v>
       </c>
     </row>
     <row r="9">
@@ -1152,64 +1149,64 @@
         <v>40</v>
       </c>
       <c r="B9" s="1">
-        <v>0.20199189275438359</v>
+        <v>0.20197528419052382</v>
       </c>
       <c r="C9" s="1">
-        <v>8.4108566866397262e-05</v>
+        <v>8.3937465188436579e-05</v>
       </c>
       <c r="D9" s="1">
-        <v>0.00035123617093761898</v>
+        <v>0.00035141362650097509</v>
       </c>
       <c r="E9" s="1">
-        <v>-0.00018777519336392291</v>
+        <v>-0.00018801348703617723</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.00036122400902767178</v>
+        <v>-0.00036110913459292196</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0002387031239584829</v>
+        <v>0.00023857686161543896</v>
       </c>
       <c r="H9" s="1">
-        <v>-1.4677537181929901e-05</v>
+        <v>-1.4819374999715371e-05</v>
       </c>
       <c r="I9" s="1">
-        <v>0.00076495029675020441</v>
+        <v>0.0007647424821385666</v>
       </c>
       <c r="J9" s="1">
-        <v>0.0021136951035538158</v>
+        <v>0.0021134861682875505</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0014172390089651266</v>
+        <v>0.0014170098432112156</v>
       </c>
       <c r="L9" s="1">
-        <v>0.0015223068942109273</v>
+        <v>0.001522078220035378</v>
       </c>
       <c r="M9" s="1">
-        <v>-4.9261892661651291e-05</v>
+        <v>-4.9262168025225898e-05</v>
       </c>
       <c r="N9" s="1">
-        <v>-3.5536222590074431e-05</v>
+        <v>-3.5533743108398248e-05</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.0001195668952252019</v>
+        <v>-0.0001195591552790498</v>
       </c>
       <c r="P9" s="1">
-        <v>-9.1438680134287541e-05</v>
+        <v>-9.1362083654490016e-05</v>
       </c>
       <c r="Q9" s="1">
-        <v>-4.9396217126893883e-07</v>
+        <v>-5.0971529881545024e-07</v>
       </c>
       <c r="R9" s="1">
-        <v>2.4037958834197126e-05</v>
+        <v>2.4099855234894704e-05</v>
       </c>
       <c r="S9" s="1">
-        <v>9.1228268514521003e-05</v>
+        <v>9.1285704955179278e-05</v>
       </c>
       <c r="T9" s="1">
-        <v>-2.1144280570890156e-05</v>
+        <v>-2.1067762430145541e-05</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.0072465954087459882</v>
+        <v>-0.0072488231281831617</v>
       </c>
     </row>
     <row r="10">
@@ -1217,64 +1214,64 @@
         <v>41</v>
       </c>
       <c r="B10" s="1">
-        <v>0.35389781114984048</v>
+        <v>0.35388142637601538</v>
       </c>
       <c r="C10" s="1">
-        <v>5.6313829347900151e-05</v>
+        <v>5.6141883848614689e-05</v>
       </c>
       <c r="D10" s="1">
-        <v>0.0004529064984716061</v>
+        <v>0.00045308314299351174</v>
       </c>
       <c r="E10" s="1">
-        <v>-0.00022839075843606848</v>
+        <v>-0.00022862838672402849</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.00051702059522755006</v>
+        <v>-0.00051690526699295857</v>
       </c>
       <c r="G10" s="1">
-        <v>0.00052291412364882097</v>
+        <v>0.00052278651984069124</v>
       </c>
       <c r="H10" s="1">
-        <v>2.6954642827969145e-05</v>
+        <v>2.6812528631533242e-05</v>
       </c>
       <c r="I10" s="1">
-        <v>0.00076985634131825054</v>
+        <v>0.00076960684787524033</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0014172390089651266</v>
+        <v>0.0014170098432112156</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0030869659804411498</v>
+        <v>0.0030867099252609937</v>
       </c>
       <c r="L10" s="1">
-        <v>0.0018038519676880005</v>
+        <v>0.001803600321956751</v>
       </c>
       <c r="M10" s="1">
-        <v>1.9360991070282866e-05</v>
+        <v>1.9361439401394467e-05</v>
       </c>
       <c r="N10" s="1">
-        <v>-7.6150534006801975e-05</v>
+        <v>-7.6147745496172106e-05</v>
       </c>
       <c r="O10" s="1">
-        <v>-1.0287754489059003e-05</v>
+        <v>-1.0279593874682478e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.0324840713446699e-05</v>
+        <v>-1.024796172507253e-05</v>
       </c>
       <c r="Q10" s="1">
-        <v>7.4042311053822531e-06</v>
+        <v>7.3884605467903109e-06</v>
       </c>
       <c r="R10" s="1">
-        <v>-0.00014697502701960762</v>
+        <v>-0.00014691311312419342</v>
       </c>
       <c r="S10" s="1">
-        <v>1.7060065606817887e-05</v>
+        <v>1.7118100749734938e-05</v>
       </c>
       <c r="T10" s="1">
-        <v>6.2577132949803368e-06</v>
+        <v>6.3355719445430496e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.0093820632512917751</v>
+        <v>-0.0093842546341940565</v>
       </c>
     </row>
     <row r="11">
@@ -1282,64 +1279,64 @@
         <v>42</v>
       </c>
       <c r="B11" s="1">
-        <v>0.33307265931656727</v>
+        <v>0.33305650095159955</v>
       </c>
       <c r="C11" s="1">
-        <v>0.00016046451498451659</v>
+        <v>0.00016029371313877063</v>
       </c>
       <c r="D11" s="1">
-        <v>0.00072104263333432929</v>
+        <v>0.00072121708751817122</v>
       </c>
       <c r="E11" s="1">
-        <v>-0.00049827710955895228</v>
+        <v>-0.00049851226117220496</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.00052019016625287368</v>
+        <v>-0.00052007537134602213</v>
       </c>
       <c r="G11" s="1">
-        <v>0.00020503189694934568</v>
+        <v>0.00020490541156619466</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.00027869788053019699</v>
+        <v>-0.00027883862833362428</v>
       </c>
       <c r="I11" s="1">
-        <v>0.00076955426923134738</v>
+        <v>0.0007693061705854005</v>
       </c>
       <c r="J11" s="1">
-        <v>0.0015223068942109273</v>
+        <v>0.001522078220035378</v>
       </c>
       <c r="K11" s="1">
-        <v>0.0018038519676880005</v>
+        <v>0.001803600321956751</v>
       </c>
       <c r="L11" s="1">
-        <v>0.004815903043138961</v>
+        <v>0.0048156436756109557</v>
       </c>
       <c r="M11" s="1">
-        <v>-0.00034716786328743091</v>
+        <v>-0.0003471660775143633</v>
       </c>
       <c r="N11" s="1">
-        <v>-0.0003952806286073821</v>
+        <v>-0.0003952779459865561</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.00033894026115626114</v>
+        <v>-0.00033893090935426667</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.00034901772939599377</v>
+        <v>-0.00034894042070791713</v>
       </c>
       <c r="Q11" s="1">
-        <v>9.2483568388658597e-07</v>
+        <v>9.0912062614367751e-07</v>
       </c>
       <c r="R11" s="1">
-        <v>-0.00017703862775723164</v>
+        <v>-0.00017697704441376957</v>
       </c>
       <c r="S11" s="1">
-        <v>4.4282069387608161e-05</v>
+        <v>4.4339396206590984e-05</v>
       </c>
       <c r="T11" s="1">
-        <v>0.00067253654298697445</v>
+        <v>0.00067261183820772202</v>
       </c>
       <c r="U11" s="1">
-        <v>-0.013401717653783552</v>
+        <v>-0.01340387654383194</v>
       </c>
     </row>
     <row r="12">
@@ -1347,64 +1344,64 @@
         <v>43</v>
       </c>
       <c r="B12" s="1">
-        <v>-0.010099725057003664</v>
+        <v>-0.010099233843579422</v>
       </c>
       <c r="C12" s="1">
-        <v>-5.3481821714562623e-05</v>
+        <v>-5.3477029643163578e-05</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.00011219925060916656</v>
+        <v>-0.00011220450394892542</v>
       </c>
       <c r="E12" s="1">
-        <v>0.00014256370933706224</v>
+        <v>0.00014257083825890138</v>
       </c>
       <c r="F12" s="1">
-        <v>-5.3350474790514598e-05</v>
+        <v>-5.3353815278029673e-05</v>
       </c>
       <c r="G12" s="1">
-        <v>5.7636201607992089e-05</v>
+        <v>5.7639053290283653e-05</v>
       </c>
       <c r="H12" s="1">
-        <v>0.00010139106771783041</v>
+        <v>0.00010139433747728623</v>
       </c>
       <c r="I12" s="1">
-        <v>-2.3848524889332769e-05</v>
+        <v>-2.3854174988041708e-05</v>
       </c>
       <c r="J12" s="1">
-        <v>-4.9261892661651291e-05</v>
+        <v>-4.9262168025225898e-05</v>
       </c>
       <c r="K12" s="1">
-        <v>1.9360991070282866e-05</v>
+        <v>1.9361439401394467e-05</v>
       </c>
       <c r="L12" s="1">
-        <v>-0.00034716786328743091</v>
+        <v>-0.0003471660775143633</v>
       </c>
       <c r="M12" s="1">
-        <v>0.0024729079924966394</v>
+        <v>0.0024729042961444147</v>
       </c>
       <c r="N12" s="1">
-        <v>0.001238606033991609</v>
+        <v>0.001238603214317014</v>
       </c>
       <c r="O12" s="1">
-        <v>0.0012241746295227562</v>
+        <v>0.0012241718265746369</v>
       </c>
       <c r="P12" s="1">
-        <v>0.0012350135711979094</v>
+        <v>0.0012350088216804842</v>
       </c>
       <c r="Q12" s="1">
-        <v>-1.6877515375656225e-05</v>
+        <v>-1.6876955686177059e-05</v>
       </c>
       <c r="R12" s="1">
-        <v>0.00011124832069316743</v>
+        <v>0.00011124602804569245</v>
       </c>
       <c r="S12" s="1">
-        <v>0.00018937622738409495</v>
+        <v>0.00018937225276977992</v>
       </c>
       <c r="T12" s="1">
-        <v>-0.00020904286941355983</v>
+        <v>-0.00020904404515773313</v>
       </c>
       <c r="U12" s="1">
-        <v>0.00084401756341118302</v>
+        <v>0.00084409160647505956</v>
       </c>
     </row>
     <row r="13">
@@ -1412,64 +1409,64 @@
         <v>44</v>
       </c>
       <c r="B13" s="1">
-        <v>-0.098453046089029092</v>
+        <v>-0.098452813257598401</v>
       </c>
       <c r="C13" s="1">
-        <v>-2.9904709081966595e-05</v>
+        <v>-2.9903678057351367e-05</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.0001042606635717337</v>
+        <v>-0.00010426163871430846</v>
       </c>
       <c r="E13" s="1">
-        <v>0.00011769018389180558</v>
+        <v>0.00011769163802135803</v>
       </c>
       <c r="F13" s="1">
-        <v>-2.8132410777834702e-05</v>
+        <v>-2.8132893629264169e-05</v>
       </c>
       <c r="G13" s="1">
-        <v>5.7975000388511827e-05</v>
+        <v>5.7973359016564831e-05</v>
       </c>
       <c r="H13" s="1">
-        <v>5.5212105297375324e-05</v>
+        <v>5.5211966803084744e-05</v>
       </c>
       <c r="I13" s="1">
-        <v>1.8699201394508307e-06</v>
+        <v>1.8716898087021595e-06</v>
       </c>
       <c r="J13" s="1">
-        <v>-3.5536222590074431e-05</v>
+        <v>-3.5533743108398248e-05</v>
       </c>
       <c r="K13" s="1">
-        <v>-7.6150534006801975e-05</v>
+        <v>-7.6147745496172106e-05</v>
       </c>
       <c r="L13" s="1">
-        <v>-0.0003952806286073821</v>
+        <v>-0.0003952779459865561</v>
       </c>
       <c r="M13" s="1">
-        <v>0.001238606033991609</v>
+        <v>0.001238603214317014</v>
       </c>
       <c r="N13" s="1">
-        <v>0.003466382371143082</v>
+        <v>0.0034663747584370349</v>
       </c>
       <c r="O13" s="1">
-        <v>0.0012268863660056591</v>
+        <v>0.0012268836288066541</v>
       </c>
       <c r="P13" s="1">
-        <v>0.0012355186718637618</v>
+        <v>0.0012355154684553767</v>
       </c>
       <c r="Q13" s="1">
-        <v>3.994110585017527e-06</v>
+        <v>3.994391408590512e-06</v>
       </c>
       <c r="R13" s="1">
-        <v>2.49597192714937e-05</v>
+        <v>2.495723682545436e-05</v>
       </c>
       <c r="S13" s="1">
-        <v>-3.060979420305913e-07</v>
+        <v>-3.084377062404452e-07</v>
       </c>
       <c r="T13" s="1">
-        <v>-0.00045551705287800499</v>
+        <v>-0.00045551853030889274</v>
       </c>
       <c r="U13" s="1">
-        <v>0.00047837471868962924</v>
+        <v>0.00047838637289130401</v>
       </c>
     </row>
     <row r="14">
@@ -1477,64 +1474,64 @@
         <v>45</v>
       </c>
       <c r="B14" s="1">
-        <v>0.0029231831168267468</v>
+        <v>0.0029232040570239246</v>
       </c>
       <c r="C14" s="1">
-        <v>-5.7648771016927882e-05</v>
+        <v>-5.7647224451053648e-05</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.00013016800957580885</v>
+        <v>-0.00013017023904562941</v>
       </c>
       <c r="E14" s="1">
-        <v>0.00015135740510381201</v>
+        <v>0.00015136043983673443</v>
       </c>
       <c r="F14" s="1">
-        <v>-3.1376406888952279e-06</v>
+        <v>-3.1391155333347284e-06</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.00011482808083704721</v>
+        <v>-0.00011482804605330508</v>
       </c>
       <c r="H14" s="1">
-        <v>3.3958497758565433e-05</v>
+        <v>3.3957744106144581e-05</v>
       </c>
       <c r="I14" s="1">
-        <v>-6.8636897057276346e-06</v>
+        <v>-6.8500681719295853e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.0001195668952252019</v>
+        <v>-0.0001195591552790498</v>
       </c>
       <c r="K14" s="1">
-        <v>-1.0287754489059003e-05</v>
+        <v>-1.0279593874682478e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>-0.00033894026115626114</v>
+        <v>-0.00033893090935426667</v>
       </c>
       <c r="M14" s="1">
-        <v>0.0012241746295227562</v>
+        <v>0.0012241718265746369</v>
       </c>
       <c r="N14" s="1">
-        <v>0.0012268863660056591</v>
+        <v>0.0012268836288066541</v>
       </c>
       <c r="O14" s="1">
-        <v>0.002476868746366232</v>
+        <v>0.0024768654400919789</v>
       </c>
       <c r="P14" s="1">
-        <v>0.0012240384681734043</v>
+        <v>0.0012240354023807722</v>
       </c>
       <c r="Q14" s="1">
-        <v>-2.030232293251617e-05</v>
+        <v>-2.0301963072558948e-05</v>
       </c>
       <c r="R14" s="1">
-        <v>0.00012532082011295403</v>
+        <v>0.00012531687455997966</v>
       </c>
       <c r="S14" s="1">
-        <v>0.00011289905966263841</v>
+        <v>0.00011289605117729008</v>
       </c>
       <c r="T14" s="1">
-        <v>-0.00022727036252296058</v>
+        <v>-0.00022727184104026513</v>
       </c>
       <c r="U14" s="1">
-        <v>0.0013058912364323307</v>
+        <v>0.0013059163080891916</v>
       </c>
     </row>
     <row r="15">
@@ -1542,64 +1539,64 @@
         <v>46</v>
       </c>
       <c r="B15" s="1">
-        <v>0.085975711454105833</v>
+        <v>0.085974401768317527</v>
       </c>
       <c r="C15" s="1">
-        <v>-7.283453152536852e-05</v>
+        <v>-7.2832730994053344e-05</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.00016217791179779298</v>
+        <v>-0.00016217959861866173</v>
       </c>
       <c r="E15" s="1">
-        <v>0.000184829284897799</v>
+        <v>0.00018483143272084515</v>
       </c>
       <c r="F15" s="1">
-        <v>-3.9756716503010084e-05</v>
+        <v>-3.9757652974542349e-05</v>
       </c>
       <c r="G15" s="1">
-        <v>0.00010122345015018601</v>
+        <v>0.00010122456430900568</v>
       </c>
       <c r="H15" s="1">
-        <v>6.7300361626277706e-05</v>
+        <v>6.7297822361575988e-05</v>
       </c>
       <c r="I15" s="1">
-        <v>-2.0931870345764609e-06</v>
+        <v>-1.945489972192345e-06</v>
       </c>
       <c r="J15" s="1">
-        <v>-9.1438680134287541e-05</v>
+        <v>-9.1362083654490016e-05</v>
       </c>
       <c r="K15" s="1">
-        <v>-1.0324840713446699e-05</v>
+        <v>-1.024796172507253e-05</v>
       </c>
       <c r="L15" s="1">
-        <v>-0.00034901772939599377</v>
+        <v>-0.00034894042070791713</v>
       </c>
       <c r="M15" s="1">
-        <v>0.0012350135711979094</v>
+        <v>0.0012350088216804842</v>
       </c>
       <c r="N15" s="1">
-        <v>0.0012355186718637618</v>
+        <v>0.0012355154684553767</v>
       </c>
       <c r="O15" s="1">
-        <v>0.0012240384681734043</v>
+        <v>0.0012240354023807722</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0016973837402095807</v>
+        <v>0.0016973802013010904</v>
       </c>
       <c r="Q15" s="1">
-        <v>-1.0472826921486856e-05</v>
+        <v>-1.047273653465468e-05</v>
       </c>
       <c r="R15" s="1">
-        <v>5.260140625687499e-05</v>
+        <v>5.260174329503012e-05</v>
       </c>
       <c r="S15" s="1">
-        <v>7.6087243032679205e-05</v>
+        <v>7.6082912812616666e-05</v>
       </c>
       <c r="T15" s="1">
-        <v>-0.0002730231730569775</v>
+        <v>-0.00027302397829684263</v>
       </c>
       <c r="U15" s="1">
-        <v>0.001652691721601141</v>
+        <v>0.0016526455380016553</v>
       </c>
     </row>
     <row r="16">
@@ -1607,64 +1604,64 @@
         <v>47</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.049701210281089779</v>
+        <v>-0.049700836054371061</v>
       </c>
       <c r="C16" s="1">
-        <v>-2.3893983448080121e-06</v>
+        <v>-2.3899475033690707e-06</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.208998261038657e-06</v>
+        <v>-1.208141924974749e-06</v>
       </c>
       <c r="E16" s="1">
-        <v>8.0144183034979409e-07</v>
+        <v>8.0050792744101179e-07</v>
       </c>
       <c r="F16" s="1">
-        <v>4.8291225436379202e-06</v>
+        <v>4.8293673665650966e-06</v>
       </c>
       <c r="G16" s="1">
-        <v>-6.9327022591181471e-06</v>
+        <v>-6.9333247933733855e-06</v>
       </c>
       <c r="H16" s="1">
-        <v>4.6302088779231923e-06</v>
+        <v>4.6306955903849755e-06</v>
       </c>
       <c r="I16" s="1">
-        <v>5.5045763964354166e-06</v>
+        <v>5.4735451849653149e-06</v>
       </c>
       <c r="J16" s="1">
-        <v>-4.9396217126893883e-07</v>
+        <v>-5.0971529881545024e-07</v>
       </c>
       <c r="K16" s="1">
-        <v>7.4042311053822531e-06</v>
+        <v>7.3884605467903109e-06</v>
       </c>
       <c r="L16" s="1">
-        <v>9.2483568388658597e-07</v>
+        <v>9.0912062614367751e-07</v>
       </c>
       <c r="M16" s="1">
-        <v>-1.6877515375656225e-05</v>
+        <v>-1.6876955686177059e-05</v>
       </c>
       <c r="N16" s="1">
-        <v>3.994110585017527e-06</v>
+        <v>3.994391408590512e-06</v>
       </c>
       <c r="O16" s="1">
-        <v>-2.030232293251617e-05</v>
+        <v>-2.0301963072558948e-05</v>
       </c>
       <c r="P16" s="1">
-        <v>-1.0472826921486856e-05</v>
+        <v>-1.047273653465468e-05</v>
       </c>
       <c r="Q16" s="1">
-        <v>3.1231180745496382e-05</v>
+        <v>3.1231113321317065e-05</v>
       </c>
       <c r="R16" s="1">
-        <v>-0.00019447768288813019</v>
+        <v>-0.00019447758534191806</v>
       </c>
       <c r="S16" s="1">
-        <v>-0.00022477962057850076</v>
+        <v>-0.00022477854564294331</v>
       </c>
       <c r="T16" s="1">
-        <v>-0.00025762978484816464</v>
+        <v>-0.00025762874202968025</v>
       </c>
       <c r="U16" s="1">
-        <v>-0.0004372298192701512</v>
+        <v>-0.00043722750283921785</v>
       </c>
     </row>
     <row r="17">
@@ -1672,64 +1669,64 @@
         <v>48</v>
       </c>
       <c r="B17" s="1">
-        <v>0.80696457203640415</v>
+        <v>0.80696278586983738</v>
       </c>
       <c r="C17" s="1">
-        <v>-3.4331258980053799e-05</v>
+        <v>-3.4331981893189511e-05</v>
       </c>
       <c r="D17" s="1">
-        <v>0.000273253830093214</v>
+        <v>0.0002732542606388149</v>
       </c>
       <c r="E17" s="1">
-        <v>-0.00030746077219194479</v>
+        <v>-0.00030746206680863294</v>
       </c>
       <c r="F17" s="1">
-        <v>6.8480303847401336e-06</v>
+        <v>6.8487392504180955e-06</v>
       </c>
       <c r="G17" s="1">
-        <v>3.0484888558718142e-05</v>
+        <v>3.0486836260596719e-05</v>
       </c>
       <c r="H17" s="1">
-        <v>0.00021615168277011815</v>
+        <v>0.0002161491637605005</v>
       </c>
       <c r="I17" s="1">
-        <v>-1.4287261285218268e-05</v>
+        <v>-1.4161555506849398e-05</v>
       </c>
       <c r="J17" s="1">
-        <v>2.4037958834197126e-05</v>
+        <v>2.4099855234894704e-05</v>
       </c>
       <c r="K17" s="1">
-        <v>-0.00014697502701960762</v>
+        <v>-0.00014691311312419342</v>
       </c>
       <c r="L17" s="1">
-        <v>-0.00017703862775723164</v>
+        <v>-0.00017697704441376957</v>
       </c>
       <c r="M17" s="1">
-        <v>0.00011124832069316743</v>
+        <v>0.00011124602804569245</v>
       </c>
       <c r="N17" s="1">
-        <v>2.49597192714937e-05</v>
+        <v>2.495723682545436e-05</v>
       </c>
       <c r="O17" s="1">
-        <v>0.00012532082011295403</v>
+        <v>0.00012531687455997966</v>
       </c>
       <c r="P17" s="1">
-        <v>5.260140625687499e-05</v>
+        <v>5.260174329503012e-05</v>
       </c>
       <c r="Q17" s="1">
-        <v>-0.00019447768288813019</v>
+        <v>-0.00019447758534191806</v>
       </c>
       <c r="R17" s="1">
-        <v>0.0068757211366015777</v>
+        <v>0.0068757056601974221</v>
       </c>
       <c r="S17" s="1">
-        <v>0.0017120715330393519</v>
+        <v>0.0017120670839557888</v>
       </c>
       <c r="T17" s="1">
-        <v>0.0018743731354633818</v>
+        <v>0.0018743694767669563</v>
       </c>
       <c r="U17" s="1">
-        <v>-0.0020538003911167732</v>
+        <v>-0.0020538654950521635</v>
       </c>
     </row>
     <row r="18">
@@ -1737,64 +1734,64 @@
         <v>49</v>
       </c>
       <c r="B18" s="1">
-        <v>1.2298484987326204</v>
+        <v>1.2298477232059279</v>
       </c>
       <c r="C18" s="1">
-        <v>1.1216810635136852e-05</v>
+        <v>1.1223884414369564e-05</v>
       </c>
       <c r="D18" s="1">
-        <v>0.00036658305620450304</v>
+        <v>0.00036657448774936319</v>
       </c>
       <c r="E18" s="1">
-        <v>-0.00036755045939226849</v>
+        <v>-0.00036753997000179423</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.00011198311530407051</v>
+        <v>-0.00011198644406670193</v>
       </c>
       <c r="G18" s="1">
-        <v>0.00063330289302006184</v>
+        <v>0.00063330689260060902</v>
       </c>
       <c r="H18" s="1">
-        <v>0.00054262593131322936</v>
+        <v>0.00054263020370422851</v>
       </c>
       <c r="I18" s="1">
-        <v>-3.9049729114890084e-05</v>
+        <v>-3.8942385664020827e-05</v>
       </c>
       <c r="J18" s="1">
-        <v>9.1228268514521003e-05</v>
+        <v>9.1285704955179278e-05</v>
       </c>
       <c r="K18" s="1">
-        <v>1.7060065606817887e-05</v>
+        <v>1.7118100749734938e-05</v>
       </c>
       <c r="L18" s="1">
-        <v>4.4282069387608161e-05</v>
+        <v>4.4339396206590984e-05</v>
       </c>
       <c r="M18" s="1">
-        <v>0.00018937622738409495</v>
+        <v>0.00018937225276977992</v>
       </c>
       <c r="N18" s="1">
-        <v>-3.060979420305913e-07</v>
+        <v>-3.084377062404452e-07</v>
       </c>
       <c r="O18" s="1">
-        <v>0.00011289905966263841</v>
+        <v>0.00011289605117729008</v>
       </c>
       <c r="P18" s="1">
-        <v>7.6087243032679205e-05</v>
+        <v>7.6082912812616666e-05</v>
       </c>
       <c r="Q18" s="1">
-        <v>-0.00022477962057850076</v>
+        <v>-0.00022477854564294331</v>
       </c>
       <c r="R18" s="1">
-        <v>0.0017120715330393519</v>
+        <v>0.0017120670839557888</v>
       </c>
       <c r="S18" s="1">
-        <v>0.0055371373176740556</v>
+        <v>0.0055371232226736717</v>
       </c>
       <c r="T18" s="1">
-        <v>0.0021867352662406185</v>
+        <v>0.0021867265086966811</v>
       </c>
       <c r="U18" s="1">
-        <v>-0.0036354034803402508</v>
+        <v>-0.0036353414917884002</v>
       </c>
     </row>
     <row r="19">
@@ -1802,64 +1799,64 @@
         <v>50</v>
       </c>
       <c r="B19" s="1">
-        <v>0.94873710003538447</v>
+        <v>0.94873570690662312</v>
       </c>
       <c r="C19" s="1">
-        <v>7.5485767162471271e-05</v>
+        <v>7.5491958015186996e-05</v>
       </c>
       <c r="D19" s="1">
-        <v>0.00054973838711235186</v>
+        <v>0.00054972589987033714</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.00057680297638266695</v>
+        <v>-0.00057678801123166659</v>
       </c>
       <c r="F19" s="1">
-        <v>-8.2459364852011455e-05</v>
+        <v>-8.2463408827555644e-05</v>
       </c>
       <c r="G19" s="1">
-        <v>0.00030295609418096717</v>
+        <v>0.00030296141407699218</v>
       </c>
       <c r="H19" s="1">
-        <v>0.00030734071911156513</v>
+        <v>0.00030734486552616656</v>
       </c>
       <c r="I19" s="1">
-        <v>-6.4911689274599937e-05</v>
+        <v>-6.4762110773726429e-05</v>
       </c>
       <c r="J19" s="1">
-        <v>-2.1144280570890156e-05</v>
+        <v>-2.1067762430145541e-05</v>
       </c>
       <c r="K19" s="1">
-        <v>6.2577132949803368e-06</v>
+        <v>6.3355719445430496e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>0.00067253654298697445</v>
+        <v>0.00067261183820772202</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.00020904286941355983</v>
+        <v>-0.00020904404515773313</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.00045551705287800499</v>
+        <v>-0.00045551853030889274</v>
       </c>
       <c r="O19" s="1">
-        <v>-0.00022727036252296058</v>
+        <v>-0.00022727184104026513</v>
       </c>
       <c r="P19" s="1">
-        <v>-0.0002730231730569775</v>
+        <v>-0.00027302397829684263</v>
       </c>
       <c r="Q19" s="1">
-        <v>-0.00025762978484816464</v>
+        <v>-0.00025762874202968025</v>
       </c>
       <c r="R19" s="1">
-        <v>0.0018743731354633818</v>
+        <v>0.0018743694767669563</v>
       </c>
       <c r="S19" s="1">
-        <v>0.0021867352662406185</v>
+        <v>0.0021867265086966811</v>
       </c>
       <c r="T19" s="1">
-        <v>0.0055314137610624247</v>
+        <v>0.005531404381623568</v>
       </c>
       <c r="U19" s="1">
-        <v>-0.0056824014590014784</v>
+        <v>-0.0056822968975799209</v>
       </c>
     </row>
     <row r="20">
@@ -1867,64 +1864,64 @@
         <v>51</v>
       </c>
       <c r="B20" s="1">
-        <v>-20.308424783015997</v>
+        <v>-20.308321852745621</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.00035346415509443388</v>
+        <v>-0.00035333537279305682</v>
       </c>
       <c r="D20" s="1">
-        <v>-0.03692271780738493</v>
+        <v>-0.03692283013729368</v>
       </c>
       <c r="E20" s="1">
-        <v>0.040298963170004795</v>
+        <v>0.040299111998440593</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.0061227718274840092</v>
+        <v>-0.0061228179805968563</v>
       </c>
       <c r="G20" s="1">
-        <v>0.0011061800288674857</v>
+        <v>0.0011060926501959465</v>
       </c>
       <c r="H20" s="1">
-        <v>-0.0096372462023258457</v>
+        <v>-0.0096371073941605087</v>
       </c>
       <c r="I20" s="1">
-        <v>-0.00062355856854435371</v>
+        <v>-0.00062800191405550142</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.0072465954087459882</v>
+        <v>-0.0072488231281831617</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.0093820632512917751</v>
+        <v>-0.0093842546341940565</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.013401717653783552</v>
+        <v>-0.01340387654383194</v>
       </c>
       <c r="M20" s="1">
-        <v>0.00084401756341118302</v>
+        <v>0.00084409160647505956</v>
       </c>
       <c r="N20" s="1">
-        <v>0.00047837471868962924</v>
+        <v>0.00047838637289130401</v>
       </c>
       <c r="O20" s="1">
-        <v>0.0013058912364323307</v>
+        <v>0.0013059163080891916</v>
       </c>
       <c r="P20" s="1">
-        <v>0.001652691721601141</v>
+        <v>0.0016526455380016553</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.0004372298192701512</v>
+        <v>-0.00043722750283921785</v>
       </c>
       <c r="R20" s="1">
-        <v>-0.0020538003911167732</v>
+        <v>-0.0020538654950521635</v>
       </c>
       <c r="S20" s="1">
-        <v>-0.0036354034803402508</v>
+        <v>-0.0036353414917884002</v>
       </c>
       <c r="T20" s="1">
-        <v>-0.0056824014590014784</v>
+        <v>-0.0056822968975799209</v>
       </c>
       <c r="U20" s="1">
-        <v>0.63053719370109795</v>
+        <v>0.63054102393515388</v>
       </c>
     </row>
   </sheetData>
@@ -1983,10 +1980,10 @@
         <v>46</v>
       </c>
       <c r="P1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" t="s">
         <v>60</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>61</v>
       </c>
       <c r="R1" t="s">
         <v>48</v>
@@ -2000,58 +1997,58 @@
         <v>33</v>
       </c>
       <c r="B2" s="1">
-        <v>-0.20210545867847657</v>
+        <v>-0.20307980535338541</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0019583566676646832</v>
+        <v>0.0019187455109253451</v>
       </c>
       <c r="D2" s="1">
-        <v>6.0920298371489956e-06</v>
+        <v>2.8691503368104659e-05</v>
       </c>
       <c r="E2" s="1">
-        <v>1.0153163501899438e-07</v>
+        <v>-1.2602598043252758e-07</v>
       </c>
       <c r="F2" s="1">
-        <v>0.00096694768631944649</v>
+        <v>0.00059965126972231998</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00052709902897711547</v>
+        <v>0.00046647797129065216</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.00016428527697770663</v>
+        <v>-0.00017180604887915977</v>
       </c>
       <c r="I2" s="1">
-        <v>2.2027173977321601e-05</v>
+        <v>3.8886397801169792e-05</v>
       </c>
       <c r="J2" s="1">
-        <v>1.2398838617618076e-05</v>
+        <v>3.8943683702290281e-05</v>
       </c>
       <c r="K2" s="1">
-        <v>2.7645801044751951e-05</v>
+        <v>0.00015449982311782569</v>
       </c>
       <c r="L2" s="1">
-        <v>-5.0860622511942125e-05</v>
+        <v>-5.2648356772774818e-05</v>
       </c>
       <c r="M2" s="1">
-        <v>0.00042533620800193968</v>
+        <v>0.0004411758728283932</v>
       </c>
       <c r="N2" s="1">
-        <v>0.00018450191404981465</v>
+        <v>0.00018593197573803932</v>
       </c>
       <c r="O2" s="1">
-        <v>3.7273994492768728e-05</v>
+        <v>2.3983706642092975e-05</v>
       </c>
       <c r="P2" s="1">
-        <v>-1.618221569238236e-05</v>
+        <v>-2.6517964146912146e-05</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.0464967098686495e-06</v>
+        <v>1.3124648126715552e-06</v>
       </c>
       <c r="R2" s="1">
-        <v>-0.00041231207262725931</v>
+        <v>-0.00039724630997625861</v>
       </c>
       <c r="S2" s="1">
-        <v>-0.0012717550900355687</v>
+        <v>-0.0015323037272553051</v>
       </c>
     </row>
     <row r="3">
@@ -2059,58 +2056,58 @@
         <v>34</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.37387905100690999</v>
+        <v>-0.37271088503398231</v>
       </c>
       <c r="C3" s="1">
-        <v>6.0920298371489956e-06</v>
+        <v>2.8691503368104659e-05</v>
       </c>
       <c r="D3" s="1">
-        <v>0.00021766986383005206</v>
+        <v>0.00021020517359122482</v>
       </c>
       <c r="E3" s="1">
-        <v>-2.2432893467670132e-06</v>
+        <v>-2.1691370064415827e-06</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.00050315322494402673</v>
+        <v>-0.00037980828634464941</v>
       </c>
       <c r="G3" s="1">
-        <v>8.6693519532699513e-05</v>
+        <v>0.00013281445911435654</v>
       </c>
       <c r="H3" s="1">
-        <v>6.0431671455317242e-05</v>
+        <v>6.3417515202394709e-05</v>
       </c>
       <c r="I3" s="1">
-        <v>7.9266350563241125e-05</v>
+        <v>6.5322770030911033e-05</v>
       </c>
       <c r="J3" s="1">
-        <v>0.00015336433062037813</v>
+        <v>0.00014776433035463318</v>
       </c>
       <c r="K3" s="1">
-        <v>-0.00011829968467690596</v>
+        <v>-0.00016417073334012939</v>
       </c>
       <c r="L3" s="1">
-        <v>-3.9481293265848086e-05</v>
+        <v>-3.9119762840081253e-05</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.00021193299465653093</v>
+        <v>-0.00022451872477230114</v>
       </c>
       <c r="N3" s="1">
-        <v>5.9569283588814526e-05</v>
+        <v>5.824139495780496e-05</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.00013025056798664344</v>
+        <v>-0.00012134295853903816</v>
       </c>
       <c r="P3" s="1">
-        <v>0.00024780047290730734</v>
+        <v>0.00025904271443509563</v>
       </c>
       <c r="Q3" s="1">
-        <v>-7.7597300108365211e-06</v>
+        <v>-8.0768541101560162e-06</v>
       </c>
       <c r="R3" s="1">
-        <v>-2.4124822636376921e-05</v>
+        <v>-3.5234862490879371e-05</v>
       </c>
       <c r="S3" s="1">
-        <v>-0.0055141799546491715</v>
+        <v>-0.0054943821524556079</v>
       </c>
     </row>
     <row r="4">
@@ -2118,58 +2115,58 @@
         <v>53</v>
       </c>
       <c r="B4" s="1">
-        <v>0.0034590768937496734</v>
+        <v>0.0034487216787919815</v>
       </c>
       <c r="C4" s="1">
-        <v>1.0153163501899438e-07</v>
+        <v>-1.2602598043252758e-07</v>
       </c>
       <c r="D4" s="1">
-        <v>-2.2432893467670132e-06</v>
+        <v>-2.1691370064415827e-06</v>
       </c>
       <c r="E4" s="1">
-        <v>2.3701272042391063e-08</v>
+        <v>2.2958532161174684e-08</v>
       </c>
       <c r="F4" s="1">
-        <v>5.9508181659736173e-06</v>
+        <v>4.8052948160413295e-06</v>
       </c>
       <c r="G4" s="1">
-        <v>-6.2536896917697691e-07</v>
+        <v>-1.0875949799289301e-06</v>
       </c>
       <c r="H4" s="1">
-        <v>-6.4620724599702954e-07</v>
+        <v>-6.7586609472770442e-07</v>
       </c>
       <c r="I4" s="1">
-        <v>-1.1694775476166615e-06</v>
+        <v>-1.0327289703867816e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>-1.4171744462281852e-06</v>
+        <v>-1.3646912633700598e-06</v>
       </c>
       <c r="K4" s="1">
-        <v>8.2205273608946151e-07</v>
+        <v>1.2685655254393189e-06</v>
       </c>
       <c r="L4" s="1">
-        <v>3.230766119063569e-07</v>
+        <v>3.1742166048356172e-07</v>
       </c>
       <c r="M4" s="1">
-        <v>1.813694432017472e-06</v>
+        <v>1.936731325838043e-06</v>
       </c>
       <c r="N4" s="1">
-        <v>-7.1180455764990214e-07</v>
+        <v>-6.9866648378298651e-07</v>
       </c>
       <c r="O4" s="1">
-        <v>1.1629577497938288e-06</v>
+        <v>1.0727428793338531e-06</v>
       </c>
       <c r="P4" s="1">
-        <v>-2.2585023743513298e-06</v>
+        <v>-2.3746237013027927e-06</v>
       </c>
       <c r="Q4" s="1">
-        <v>7.0944241413777134e-08</v>
+        <v>7.422017117009271e-08</v>
       </c>
       <c r="R4" s="1">
-        <v>-5.6776515873981797e-08</v>
+        <v>6.3301205760971774e-08</v>
       </c>
       <c r="S4" s="1">
-        <v>5.4418517153837962e-05</v>
+        <v>5.4269536274016694e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2177,58 +2174,58 @@
         <v>54</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.42578419414402074</v>
+        <v>-0.46077624299324543</v>
       </c>
       <c r="C5" s="1">
-        <v>0.00096694768631944649</v>
+        <v>0.00059965126972231998</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.00050315322494402673</v>
+        <v>-0.00037980828634464941</v>
       </c>
       <c r="E5" s="1">
-        <v>5.9508181659736173e-06</v>
+        <v>4.8052948160413295e-06</v>
       </c>
       <c r="F5" s="1">
-        <v>0.012773098474732087</v>
+        <v>0.01254130362749524</v>
       </c>
       <c r="G5" s="1">
-        <v>0.001318396162538856</v>
+        <v>0.00057155949167475746</v>
       </c>
       <c r="H5" s="1">
-        <v>0.00058718792630792389</v>
+        <v>0.00054980788672999784</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.00043240436366985806</v>
+        <v>-0.00021806724196447532</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.00061600975009284465</v>
+        <v>-0.00049970615802045256</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.0038914905442609159</v>
+        <v>-0.0035931014499431479</v>
       </c>
       <c r="L5" s="1">
-        <v>-0.00060679619353676121</v>
+        <v>-0.00069897213842377501</v>
       </c>
       <c r="M5" s="1">
-        <v>0.0005163998974247702</v>
+        <v>0.00072472404986112255</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.0011350501115755711</v>
+        <v>-0.0012171152751150396</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.00032121829128296938</v>
+        <v>-0.00057945386650328379</v>
       </c>
       <c r="P5" s="1">
-        <v>0.00093804391939090266</v>
+        <v>0.00085905830702285722</v>
       </c>
       <c r="Q5" s="1">
-        <v>-2.8034997208915286e-05</v>
+        <v>-2.6007236537108405e-05</v>
       </c>
       <c r="R5" s="1">
-        <v>-0.000764162732341837</v>
+        <v>-0.00059188322901794661</v>
       </c>
       <c r="S5" s="1">
-        <v>5.5748127155249433e-05</v>
+        <v>-0.0011235534183665803</v>
       </c>
     </row>
     <row r="6">
@@ -2236,58 +2233,58 @@
         <v>55</v>
       </c>
       <c r="B6" s="1">
-        <v>0.081760386906955612</v>
+        <v>0.078304599542761325</v>
       </c>
       <c r="C6" s="1">
-        <v>0.00052709902897711547</v>
+        <v>0.00046647797129065216</v>
       </c>
       <c r="D6" s="1">
-        <v>8.6693519532699513e-05</v>
+        <v>0.00013281445911435654</v>
       </c>
       <c r="E6" s="1">
-        <v>-6.2536896917697691e-07</v>
+        <v>-1.0875949799289301e-06</v>
       </c>
       <c r="F6" s="1">
-        <v>0.001318396162538856</v>
+        <v>0.00057155949167475746</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0074751326992771594</v>
+        <v>0.0074436922064758763</v>
       </c>
       <c r="H6" s="1">
-        <v>0.001151959316993094</v>
+        <v>0.0011497748110105282</v>
       </c>
       <c r="I6" s="1">
-        <v>-1.0844507450832094e-05</v>
+        <v>1.1949542818954638e-05</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.00013179041247934182</v>
+        <v>-7.5320630599762407e-05</v>
       </c>
       <c r="K6" s="1">
-        <v>-0.0008252541816774451</v>
+        <v>-0.00060185241040790227</v>
       </c>
       <c r="L6" s="1">
-        <v>0.00010311343969316691</v>
+        <v>0.00010098596203780396</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.00014821588108112098</v>
+        <v>-0.00011730376109023448</v>
       </c>
       <c r="N6" s="1">
-        <v>0.00067157872967002941</v>
+        <v>0.0006712491304428931</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.00035879868940092026</v>
+        <v>-0.00037059678599975839</v>
       </c>
       <c r="P6" s="1">
-        <v>0.0011758600929203231</v>
+        <v>0.0011687798515567197</v>
       </c>
       <c r="Q6" s="1">
-        <v>-3.6079906662757511e-05</v>
+        <v>-3.5936496323738675e-05</v>
       </c>
       <c r="R6" s="1">
-        <v>-4.0693742417292206e-05</v>
+        <v>-2.094508534483154e-05</v>
       </c>
       <c r="S6" s="1">
-        <v>-0.01187828565425722</v>
+        <v>-0.012550715087855456</v>
       </c>
     </row>
     <row r="7">
@@ -2295,58 +2292,58 @@
         <v>56</v>
       </c>
       <c r="B7" s="1">
-        <v>0.41235445201670917</v>
+        <v>0.41182282124865077</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.00016428527697770663</v>
+        <v>-0.00017180604887915977</v>
       </c>
       <c r="D7" s="1">
-        <v>6.0431671455317242e-05</v>
+        <v>6.3417515202394709e-05</v>
       </c>
       <c r="E7" s="1">
-        <v>-6.4620724599702954e-07</v>
+        <v>-6.7586609472770442e-07</v>
       </c>
       <c r="F7" s="1">
-        <v>0.00058718792630792389</v>
+        <v>0.00054980788672999784</v>
       </c>
       <c r="G7" s="1">
-        <v>0.001151959316993094</v>
+        <v>0.0011497748110105282</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0018595060900029182</v>
+        <v>0.0018630172026439166</v>
       </c>
       <c r="I7" s="1">
-        <v>-0.0003198856619453321</v>
+        <v>-0.00032169317310383732</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.00022081640180901193</v>
+        <v>-0.00021942334240353996</v>
       </c>
       <c r="K7" s="1">
-        <v>-0.00011140574328799628</v>
+        <v>-9.1069295380637422e-05</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.00019143588389744753</v>
+        <v>-0.00019522767011602503</v>
       </c>
       <c r="M7" s="1">
-        <v>-0.00049199341931383098</v>
+        <v>-0.00049138523768405419</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.00021799491409870255</v>
+        <v>-0.00022037933265533767</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.0002069149096294811</v>
+        <v>-0.00021061120924761509</v>
       </c>
       <c r="P7" s="1">
-        <v>0.00018232649438575089</v>
+        <v>0.00018220140931863942</v>
       </c>
       <c r="Q7" s="1">
-        <v>-6.147743283889975e-06</v>
+        <v>-6.1533758553537324e-06</v>
       </c>
       <c r="R7" s="1">
-        <v>0.00035116691694036303</v>
+        <v>0.00035886186608150841</v>
       </c>
       <c r="S7" s="1">
-        <v>-0.0027022747096915496</v>
+        <v>-0.0027403716128960275</v>
       </c>
     </row>
     <row r="8">
@@ -2354,58 +2351,58 @@
         <v>57</v>
       </c>
       <c r="B8" s="1">
-        <v>0.6289270643682936</v>
+        <v>0.63163681848877895</v>
       </c>
       <c r="C8" s="1">
-        <v>2.2027173977321601e-05</v>
+        <v>3.8886397801169792e-05</v>
       </c>
       <c r="D8" s="1">
-        <v>7.9266350563241125e-05</v>
+        <v>6.5322770030911033e-05</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.1694775476166615e-06</v>
+        <v>-1.0327289703867816e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.00043240436366985806</v>
+        <v>-0.00021806724196447532</v>
       </c>
       <c r="G8" s="1">
-        <v>-1.0844507450832094e-05</v>
+        <v>1.1949542818954638e-05</v>
       </c>
       <c r="H8" s="1">
-        <v>-0.0003198856619453321</v>
+        <v>-0.00032169317310383732</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0026862448815902777</v>
+        <v>0.0026825526604967605</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.00016014450962899163</v>
+        <v>-0.00017755539622060613</v>
       </c>
       <c r="K8" s="1">
-        <v>8.5174009747019172e-05</v>
+        <v>1.5405631469594448e-05</v>
       </c>
       <c r="L8" s="1">
-        <v>5.0220848520146551e-05</v>
+        <v>5.3505130714296236e-05</v>
       </c>
       <c r="M8" s="1">
-        <v>3.9001150218729642e-05</v>
+        <v>2.7187905144246416e-05</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.00018417608330000855</v>
+        <v>-0.00017922546289716787</v>
       </c>
       <c r="O8" s="1">
-        <v>0.00012122929599303646</v>
+        <v>0.00012963454819835889</v>
       </c>
       <c r="P8" s="1">
-        <v>-0.00027572101216450832</v>
+        <v>-0.00027411815396606245</v>
       </c>
       <c r="Q8" s="1">
-        <v>8.834185140405489e-06</v>
+        <v>8.8096063857446903e-06</v>
       </c>
       <c r="R8" s="1">
-        <v>0.00068351974443641209</v>
+        <v>0.00067720387709269223</v>
       </c>
       <c r="S8" s="1">
-        <v>-0.00094395294513215534</v>
+        <v>-0.00073944865254556551</v>
       </c>
     </row>
     <row r="9">
@@ -2413,58 +2410,58 @@
         <v>58</v>
       </c>
       <c r="B9" s="1">
-        <v>0.16731837087619861</v>
+        <v>0.16992003561758315</v>
       </c>
       <c r="C9" s="1">
-        <v>1.2398838617618076e-05</v>
+        <v>3.8943683702290281e-05</v>
       </c>
       <c r="D9" s="1">
-        <v>0.00015336433062037813</v>
+        <v>0.00014776433035463318</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.4171744462281852e-06</v>
+        <v>-1.3646912633700598e-06</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.00061600975009284465</v>
+        <v>-0.00049970615802045256</v>
       </c>
       <c r="G9" s="1">
-        <v>-0.00013179041247934182</v>
+        <v>-7.5320630599762407e-05</v>
       </c>
       <c r="H9" s="1">
-        <v>-0.00022081640180901193</v>
+        <v>-0.00021942334240353996</v>
       </c>
       <c r="I9" s="1">
-        <v>-0.00016014450962899163</v>
+        <v>-0.00017755539622060613</v>
       </c>
       <c r="J9" s="1">
-        <v>0.00057830056528428348</v>
+        <v>0.00057765222759959152</v>
       </c>
       <c r="K9" s="1">
-        <v>-0.00043465170906281886</v>
+        <v>-0.00049144816772096994</v>
       </c>
       <c r="L9" s="1">
-        <v>-5.1124506252735419e-05</v>
+        <v>-5.0113828306216652e-05</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.00016563265067671539</v>
+        <v>-0.00018370654704310532</v>
       </c>
       <c r="N9" s="1">
-        <v>-9.8239290916555568e-06</v>
+        <v>-9.0003705362128256e-06</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.00011629110063202959</v>
+        <v>-0.00010505651355663436</v>
       </c>
       <c r="P9" s="1">
-        <v>9.9460042705175008e-05</v>
+        <v>0.00011180392911405376</v>
       </c>
       <c r="Q9" s="1">
-        <v>-3.0323729677532163e-06</v>
+        <v>-3.3784268481783247e-06</v>
       </c>
       <c r="R9" s="1">
-        <v>-0.00012641094781376929</v>
+        <v>-0.00014141822764368898</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.0033514147143298458</v>
+        <v>-0.0033713595457167825</v>
       </c>
     </row>
     <row r="10">
@@ -2472,58 +2469,58 @@
         <v>59</v>
       </c>
       <c r="B10" s="1">
-        <v>-0.45495177724702018</v>
+        <v>-0.44944904046095269</v>
       </c>
       <c r="C10" s="1">
-        <v>2.7645801044751951e-05</v>
+        <v>0.00015449982311782569</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.00011829968467690596</v>
+        <v>-0.00016417073334012939</v>
       </c>
       <c r="E10" s="1">
-        <v>8.2205273608946151e-07</v>
+        <v>1.2685655254393189e-06</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.0038914905442609159</v>
+        <v>-0.0035931014499431479</v>
       </c>
       <c r="G10" s="1">
-        <v>-0.0008252541816774451</v>
+        <v>-0.00060185241040790227</v>
       </c>
       <c r="H10" s="1">
-        <v>-0.00011140574328799628</v>
+        <v>-9.1069295380637422e-05</v>
       </c>
       <c r="I10" s="1">
-        <v>8.5174009747019172e-05</v>
+        <v>1.5405631469594448e-05</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.00043465170906281886</v>
+        <v>-0.00049144816772096994</v>
       </c>
       <c r="K10" s="1">
-        <v>0.011813482754980295</v>
+        <v>0.011953734163144042</v>
       </c>
       <c r="L10" s="1">
-        <v>0.00025932465727595199</v>
+        <v>0.00027949406197858701</v>
       </c>
       <c r="M10" s="1">
-        <v>0.00083804991333277172</v>
+        <v>0.00079435791441675833</v>
       </c>
       <c r="N10" s="1">
-        <v>0.00013434279336983681</v>
+        <v>0.00013864655031700852</v>
       </c>
       <c r="O10" s="1">
-        <v>0.00028005298312466147</v>
+        <v>0.00035258125370861806</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.00015531246888984937</v>
+        <v>-0.0001134163410300875</v>
       </c>
       <c r="Q10" s="1">
-        <v>6.0824885602483168e-06</v>
+        <v>4.9151507647043313e-06</v>
       </c>
       <c r="R10" s="1">
-        <v>8.1642425871449259e-05</v>
+        <v>1.8557524785653293e-05</v>
       </c>
       <c r="S10" s="1">
-        <v>0.0027341720449894765</v>
+        <v>0.0030808632935195044</v>
       </c>
     </row>
     <row r="11">
@@ -2531,58 +2528,58 @@
         <v>43</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.054903148397025196</v>
+        <v>-0.053334932848202898</v>
       </c>
       <c r="C11" s="1">
-        <v>-5.0860622511942125e-05</v>
+        <v>-5.2648356772774818e-05</v>
       </c>
       <c r="D11" s="1">
-        <v>-3.9481293265848086e-05</v>
+        <v>-3.9119762840081253e-05</v>
       </c>
       <c r="E11" s="1">
-        <v>3.230766119063569e-07</v>
+        <v>3.1742166048356172e-07</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.00060679619353676121</v>
+        <v>-0.00069897213842377501</v>
       </c>
       <c r="G11" s="1">
-        <v>0.00010311343969316691</v>
+        <v>0.00010098596203780396</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.00019143588389744753</v>
+        <v>-0.00019522767011602503</v>
       </c>
       <c r="I11" s="1">
-        <v>5.0220848520146551e-05</v>
+        <v>5.3505130714296236e-05</v>
       </c>
       <c r="J11" s="1">
-        <v>-5.1124506252735419e-05</v>
+        <v>-5.0113828306216652e-05</v>
       </c>
       <c r="K11" s="1">
-        <v>0.00025932465727595199</v>
+        <v>0.00027949406197858701</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0044643682166080126</v>
+        <v>0.0044754263760663632</v>
       </c>
       <c r="M11" s="1">
-        <v>0.0022276423794305158</v>
+        <v>0.0022331967861154186</v>
       </c>
       <c r="N11" s="1">
-        <v>0.0021391492399866169</v>
+        <v>0.002147728224898247</v>
       </c>
       <c r="O11" s="1">
-        <v>0.0021521934605003494</v>
+        <v>0.0021569114547898985</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.00029124554085765243</v>
+        <v>-0.00030024453109018482</v>
       </c>
       <c r="Q11" s="1">
-        <v>8.3624700118942581e-06</v>
+        <v>8.6377670548199235e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>0.0001083513492967466</v>
+        <v>0.00010814028944914933</v>
       </c>
       <c r="S11" s="1">
-        <v>0.0010966169175131014</v>
+        <v>0.001155961318785194</v>
       </c>
     </row>
     <row r="12">
@@ -2590,58 +2587,58 @@
         <v>44</v>
       </c>
       <c r="B12" s="1">
-        <v>0.21507312756926589</v>
+        <v>0.21733603101787544</v>
       </c>
       <c r="C12" s="1">
-        <v>0.00042533620800193968</v>
+        <v>0.0004411758728283932</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.00021193299465653093</v>
+        <v>-0.00022451872477230114</v>
       </c>
       <c r="E12" s="1">
-        <v>1.813694432017472e-06</v>
+        <v>1.936731325838043e-06</v>
       </c>
       <c r="F12" s="1">
-        <v>0.0005163998974247702</v>
+        <v>0.00072472404986112255</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00014821588108112098</v>
+        <v>-0.00011730376109023448</v>
       </c>
       <c r="H12" s="1">
-        <v>-0.00049199341931383098</v>
+        <v>-0.00049138523768405419</v>
       </c>
       <c r="I12" s="1">
-        <v>3.9001150218729642e-05</v>
+        <v>2.7187905144246416e-05</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.00016563265067671539</v>
+        <v>-0.00018370654704310532</v>
       </c>
       <c r="K12" s="1">
-        <v>0.00083804991333277172</v>
+        <v>0.00079435791441675833</v>
       </c>
       <c r="L12" s="1">
-        <v>0.0022276423794305158</v>
+        <v>0.0022331967861154186</v>
       </c>
       <c r="M12" s="1">
-        <v>0.0089407075220182559</v>
+        <v>0.0089480763430979087</v>
       </c>
       <c r="N12" s="1">
-        <v>0.002155886174439979</v>
+        <v>0.0021623006183740805</v>
       </c>
       <c r="O12" s="1">
-        <v>0.0021617314671274423</v>
+        <v>0.0021710200870012739</v>
       </c>
       <c r="P12" s="1">
-        <v>-0.0011427698400908778</v>
+        <v>-0.0011458395867546926</v>
       </c>
       <c r="Q12" s="1">
-        <v>3.8210113880115944e-05</v>
+        <v>3.8338991677671259e-05</v>
       </c>
       <c r="R12" s="1">
-        <v>-0.00077811059689838493</v>
+        <v>-0.00077915630462938577</v>
       </c>
       <c r="S12" s="1">
-        <v>0.0094178769331026962</v>
+        <v>0.0096393186343032324</v>
       </c>
     </row>
     <row r="13">
@@ -2649,58 +2646,58 @@
         <v>45</v>
       </c>
       <c r="B13" s="1">
-        <v>0.05279545662625381</v>
+        <v>0.053934294454917708</v>
       </c>
       <c r="C13" s="1">
-        <v>0.00018450191404981465</v>
+        <v>0.00018593197573803932</v>
       </c>
       <c r="D13" s="1">
-        <v>5.9569283588814526e-05</v>
+        <v>5.824139495780496e-05</v>
       </c>
       <c r="E13" s="1">
-        <v>-7.1180455764990214e-07</v>
+        <v>-6.9866648378298651e-07</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.0011350501115755711</v>
+        <v>-0.0012171152751150396</v>
       </c>
       <c r="G13" s="1">
-        <v>0.00067157872967002941</v>
+        <v>0.0006712491304428931</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.00021799491409870255</v>
+        <v>-0.00022037933265533767</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.00018417608330000855</v>
+        <v>-0.00017922546289716787</v>
       </c>
       <c r="J13" s="1">
-        <v>-9.8239290916555568e-06</v>
+        <v>-9.0003705362128256e-06</v>
       </c>
       <c r="K13" s="1">
-        <v>0.00013434279336983681</v>
+        <v>0.00013864655031700852</v>
       </c>
       <c r="L13" s="1">
-        <v>0.0021391492399866169</v>
+        <v>0.002147728224898247</v>
       </c>
       <c r="M13" s="1">
-        <v>0.002155886174439979</v>
+        <v>0.0021623006183740805</v>
       </c>
       <c r="N13" s="1">
-        <v>0.0052836965244112064</v>
+        <v>0.0052965018217267833</v>
       </c>
       <c r="O13" s="1">
-        <v>0.0020997637566048163</v>
+        <v>0.0021034879521508944</v>
       </c>
       <c r="P13" s="1">
-        <v>0.00036472749023815386</v>
+        <v>0.00035342551209506225</v>
       </c>
       <c r="Q13" s="1">
-        <v>-1.1573948523418212e-05</v>
+        <v>-1.1227906766428873e-05</v>
       </c>
       <c r="R13" s="1">
-        <v>-2.3164290007667183e-05</v>
+        <v>-2.5227374123561457e-05</v>
       </c>
       <c r="S13" s="1">
-        <v>-0.0056343058495876086</v>
+        <v>-0.0055363028195175188</v>
       </c>
     </row>
     <row r="14">
@@ -2708,176 +2705,176 @@
         <v>46</v>
       </c>
       <c r="B14" s="1">
-        <v>0.22390012099905202</v>
+        <v>0.22397401586085075</v>
       </c>
       <c r="C14" s="1">
-        <v>3.7273994492768728e-05</v>
+        <v>2.3983706642092975e-05</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.00013025056798664344</v>
+        <v>-0.00012134295853903816</v>
       </c>
       <c r="E14" s="1">
-        <v>1.1629577497938288e-06</v>
+        <v>1.0727428793338531e-06</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.00032121829128296938</v>
+        <v>-0.00057945386650328379</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.00035879868940092026</v>
+        <v>-0.00037059678599975839</v>
       </c>
       <c r="H14" s="1">
-        <v>-0.0002069149096294811</v>
+        <v>-0.00021061120924761509</v>
       </c>
       <c r="I14" s="1">
-        <v>0.00012122929599303646</v>
+        <v>0.00012963454819835889</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.00011629110063202959</v>
+        <v>-0.00010505651355663436</v>
       </c>
       <c r="K14" s="1">
-        <v>0.00028005298312466147</v>
+        <v>0.00035258125370861806</v>
       </c>
       <c r="L14" s="1">
-        <v>0.0021521934605003494</v>
+        <v>0.0021569114547898985</v>
       </c>
       <c r="M14" s="1">
-        <v>0.0021617314671274423</v>
+        <v>0.0021710200870012739</v>
       </c>
       <c r="N14" s="1">
-        <v>0.0020997637566048163</v>
+        <v>0.0021034879521508944</v>
       </c>
       <c r="O14" s="1">
-        <v>0.0033060966698744629</v>
+        <v>0.0033100237674944175</v>
       </c>
       <c r="P14" s="1">
-        <v>-0.00028501995420284642</v>
+        <v>-0.00029961009131618927</v>
       </c>
       <c r="Q14" s="1">
-        <v>8.6552681030033729e-06</v>
+        <v>9.0690396581683143e-06</v>
       </c>
       <c r="R14" s="1">
-        <v>0.00030050257909776574</v>
+        <v>0.00030092282014015909</v>
       </c>
       <c r="S14" s="1">
-        <v>0.0023555695555759091</v>
+        <v>0.0023300139391132478</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.31553104949630212</v>
+        <v>-0.31604155792026462</v>
       </c>
       <c r="C15" s="1">
-        <v>-1.618221569238236e-05</v>
+        <v>-2.6517964146912146e-05</v>
       </c>
       <c r="D15" s="1">
-        <v>0.00024780047290730734</v>
+        <v>0.00025904271443509563</v>
       </c>
       <c r="E15" s="1">
-        <v>-2.2585023743513298e-06</v>
+        <v>-2.3746237013027927e-06</v>
       </c>
       <c r="F15" s="1">
-        <v>0.00093804391939090266</v>
+        <v>0.00085905830702285722</v>
       </c>
       <c r="G15" s="1">
-        <v>0.0011758600929203231</v>
+        <v>0.0011687798515567197</v>
       </c>
       <c r="H15" s="1">
-        <v>0.00018232649438575089</v>
+        <v>0.00018220140931863942</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.00027572101216450832</v>
+        <v>-0.00027411815396606245</v>
       </c>
       <c r="J15" s="1">
-        <v>9.9460042705175008e-05</v>
+        <v>0.00011180392911405376</v>
       </c>
       <c r="K15" s="1">
-        <v>-0.00015531246888984937</v>
+        <v>-0.0001134163410300875</v>
       </c>
       <c r="L15" s="1">
-        <v>-0.00029124554085765243</v>
+        <v>-0.00030024453109018482</v>
       </c>
       <c r="M15" s="1">
-        <v>-0.0011427698400908778</v>
+        <v>-0.0011458395867546926</v>
       </c>
       <c r="N15" s="1">
-        <v>0.00036472749023815386</v>
+        <v>0.00035342551209506225</v>
       </c>
       <c r="O15" s="1">
-        <v>-0.00028501995420284642</v>
+        <v>-0.00029961009131618927</v>
       </c>
       <c r="P15" s="1">
-        <v>0.004029326163929447</v>
+        <v>0.0040288622653894754</v>
       </c>
       <c r="Q15" s="1">
-        <v>-0.0001214504059162871</v>
+        <v>-0.00012148420821883785</v>
       </c>
       <c r="R15" s="1">
-        <v>0.00014900696449767284</v>
+        <v>0.00016128938304163509</v>
       </c>
       <c r="S15" s="1">
-        <v>-0.035788121061866483</v>
+        <v>-0.035942137966643889</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1">
-        <v>0.010582240239214599</v>
+        <v>0.01060082832379251</v>
       </c>
       <c r="C16" s="1">
-        <v>1.0464967098686495e-06</v>
+        <v>1.3124648126715552e-06</v>
       </c>
       <c r="D16" s="1">
-        <v>-7.7597300108365211e-06</v>
+        <v>-8.0768541101560162e-06</v>
       </c>
       <c r="E16" s="1">
-        <v>7.0944241413777134e-08</v>
+        <v>7.422017117009271e-08</v>
       </c>
       <c r="F16" s="1">
-        <v>-2.8034997208915286e-05</v>
+        <v>-2.6007236537108405e-05</v>
       </c>
       <c r="G16" s="1">
-        <v>-3.6079906662757511e-05</v>
+        <v>-3.5936496323738675e-05</v>
       </c>
       <c r="H16" s="1">
-        <v>-6.147743283889975e-06</v>
+        <v>-6.1533758553537324e-06</v>
       </c>
       <c r="I16" s="1">
-        <v>8.834185140405489e-06</v>
+        <v>8.8096063857446903e-06</v>
       </c>
       <c r="J16" s="1">
-        <v>-3.0323729677532163e-06</v>
+        <v>-3.3784268481783247e-06</v>
       </c>
       <c r="K16" s="1">
-        <v>6.0824885602483168e-06</v>
+        <v>4.9151507647043313e-06</v>
       </c>
       <c r="L16" s="1">
-        <v>8.3624700118942581e-06</v>
+        <v>8.6377670548199235e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>3.8210113880115944e-05</v>
+        <v>3.8338991677671259e-05</v>
       </c>
       <c r="N16" s="1">
-        <v>-1.1573948523418212e-05</v>
+        <v>-1.1227906766428873e-05</v>
       </c>
       <c r="O16" s="1">
-        <v>8.6552681030033729e-06</v>
+        <v>9.0690396581683143e-06</v>
       </c>
       <c r="P16" s="1">
-        <v>-0.0001214504059162871</v>
+        <v>-0.00012148420821883785</v>
       </c>
       <c r="Q16" s="1">
-        <v>3.6953175894466673e-06</v>
+        <v>3.6977574448080565e-06</v>
       </c>
       <c r="R16" s="1">
-        <v>-1.0382673561314874e-05</v>
+        <v>-1.0745236252207623e-05</v>
       </c>
       <c r="S16" s="1">
-        <v>0.0010739279504812195</v>
+        <v>0.0010786155006250497</v>
       </c>
     </row>
     <row r="17">
@@ -2885,58 +2882,58 @@
         <v>48</v>
       </c>
       <c r="B17" s="1">
-        <v>0.53700486658264579</v>
+        <v>0.53454518593422673</v>
       </c>
       <c r="C17" s="1">
-        <v>-0.00041231207262725931</v>
+        <v>-0.00039724630997625861</v>
       </c>
       <c r="D17" s="1">
-        <v>-2.4124822636376921e-05</v>
+        <v>-3.5234862490879371e-05</v>
       </c>
       <c r="E17" s="1">
-        <v>-5.6776515873981797e-08</v>
+        <v>6.3301205760971774e-08</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.000764162732341837</v>
+        <v>-0.00059188322901794661</v>
       </c>
       <c r="G17" s="1">
-        <v>-4.0693742417292206e-05</v>
+        <v>-2.094508534483154e-05</v>
       </c>
       <c r="H17" s="1">
-        <v>0.00035116691694036303</v>
+        <v>0.00035886186608150841</v>
       </c>
       <c r="I17" s="1">
-        <v>0.00068351974443641209</v>
+        <v>0.00067720387709269223</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.00012641094781376929</v>
+        <v>-0.00014141822764368898</v>
       </c>
       <c r="K17" s="1">
-        <v>8.1642425871449259e-05</v>
+        <v>1.8557524785653293e-05</v>
       </c>
       <c r="L17" s="1">
-        <v>0.0001083513492967466</v>
+        <v>0.00010814028944914933</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.00077811059689838493</v>
+        <v>-0.00077915630462938577</v>
       </c>
       <c r="N17" s="1">
-        <v>-2.3164290007667183e-05</v>
+        <v>-2.5227374123561457e-05</v>
       </c>
       <c r="O17" s="1">
-        <v>0.00030050257909776574</v>
+        <v>0.00030092282014015909</v>
       </c>
       <c r="P17" s="1">
-        <v>0.00014900696449767284</v>
+        <v>0.00016128938304163509</v>
       </c>
       <c r="Q17" s="1">
-        <v>-1.0382673561314874e-05</v>
+        <v>-1.0745236252207623e-05</v>
       </c>
       <c r="R17" s="1">
-        <v>0.0058500006161129915</v>
+        <v>0.0058613012049222018</v>
       </c>
       <c r="S17" s="1">
-        <v>1.8353038363623292e-05</v>
+        <v>9.0123679709935584e-05</v>
       </c>
     </row>
     <row r="18">
@@ -2944,58 +2941,58 @@
         <v>51</v>
       </c>
       <c r="B18" s="1">
-        <v>6.8603049231749269</v>
+        <v>6.8401276302415077</v>
       </c>
       <c r="C18" s="1">
-        <v>-0.0012717550900355687</v>
+        <v>-0.0015323037272553051</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.0055141799546491715</v>
+        <v>-0.0054943821524556079</v>
       </c>
       <c r="E18" s="1">
-        <v>5.4418517153837962e-05</v>
+        <v>5.4269536274016694e-05</v>
       </c>
       <c r="F18" s="1">
-        <v>5.5748127155249433e-05</v>
+        <v>-0.0011235534183665803</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.01187828565425722</v>
+        <v>-0.012550715087855456</v>
       </c>
       <c r="H18" s="1">
-        <v>-0.0027022747096915496</v>
+        <v>-0.0027403716128960275</v>
       </c>
       <c r="I18" s="1">
-        <v>-0.00094395294513215534</v>
+        <v>-0.00073944865254556551</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.0033514147143298458</v>
+        <v>-0.0033713595457167825</v>
       </c>
       <c r="K18" s="1">
-        <v>0.0027341720449894765</v>
+        <v>0.0030808632935195044</v>
       </c>
       <c r="L18" s="1">
-        <v>0.0010966169175131014</v>
+        <v>0.001155961318785194</v>
       </c>
       <c r="M18" s="1">
-        <v>0.0094178769331026962</v>
+        <v>0.0096393186343032324</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.0056343058495876086</v>
+        <v>-0.0055363028195175188</v>
       </c>
       <c r="O18" s="1">
-        <v>0.0023555695555759091</v>
+        <v>0.0023300139391132478</v>
       </c>
       <c r="P18" s="1">
-        <v>-0.035788121061866483</v>
+        <v>-0.035942137966643889</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.0010739279504812195</v>
+        <v>0.0010786155006250497</v>
       </c>
       <c r="R18" s="1">
-        <v>1.8353038363623292e-05</v>
+        <v>9.0123679709935584e-05</v>
       </c>
       <c r="S18" s="1">
-        <v>0.37910139412122301</v>
+        <v>0.37998499901018346</v>
       </c>
     </row>
   </sheetData>
@@ -3015,57 +3012,57 @@
         <v>52</v>
       </c>
       <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>68</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>69</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>70</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>71</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>72</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>74</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>76</v>
-      </c>
-      <c r="R1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2">
         <v>-0.048492417600928997</v>
@@ -3121,7 +3118,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" s="2">
         <v>0.1119637886343586</v>
@@ -3177,7 +3174,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="2">
         <v>0.015814099963073567</v>
@@ -3233,7 +3230,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="2">
         <v>-0.19307100155893817</v>
@@ -3289,7 +3286,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2">
         <v>-0.31621923146961251</v>
@@ -3345,7 +3342,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2">
         <v>-0.21488549050583861</v>
@@ -3401,7 +3398,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2">
         <v>-0.13658901231515999</v>
@@ -3457,7 +3454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2">
         <v>0.18640381066811282</v>
@@ -3513,7 +3510,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2">
         <v>-0.0066075553534049748</v>
@@ -3569,7 +3566,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="2">
         <v>-0.61312845869547283</v>
@@ -3625,7 +3622,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="2">
         <v>-7.819005525547813</v>
@@ -3681,7 +3678,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" s="2">
         <v>-0.57366523018618643</v>
@@ -3737,7 +3734,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2">
         <v>-1.726532244359815</v>
@@ -3793,7 +3790,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2">
         <v>0.050042998474953589</v>
@@ -3849,7 +3846,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2">
         <v>0.22337779378170336</v>
@@ -3905,7 +3902,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2">
         <v>11.570207623900812</v>
